--- a/RPGProject/Assets/Project/Data/ExcelData/InfoEnum.xlsx
+++ b/RPGProject/Assets/Project/Data/ExcelData/InfoEnum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suyb1\Documents\GitHub\RPG\RPGProject\Assets\Project\Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70DD00CC-C461-4868-8AAC-9A1C253819A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195B18FA-46BB-400E-9745-003CCF7B1E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="6690" windowWidth="16485" windowHeight="8715" xr2:uid="{69A6533B-D580-4E18-8919-764171C47CAB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{69A6533B-D580-4E18-8919-764171C47CAB}"/>
   </bookViews>
   <sheets>
     <sheet name="CSVEnums" sheetId="1" r:id="rId1"/>

--- a/RPGProject/Assets/Project/Data/ExcelData/InfoEnum.xlsx
+++ b/RPGProject/Assets/Project/Data/ExcelData/InfoEnum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suyb1\Documents\GitHub\RPG\RPGProject\Assets\Project\Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195B18FA-46BB-400E-9745-003CCF7B1E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E497EB52-31B1-441F-9242-27BCDA1D0DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{69A6533B-D580-4E18-8919-764171C47CAB}"/>
+    <workbookView xWindow="1230" yWindow="765" windowWidth="14790" windowHeight="10695" xr2:uid="{69A6533B-D580-4E18-8919-764171C47CAB}"/>
   </bookViews>
   <sheets>
     <sheet name="CSVEnums" sheetId="1" r:id="rId1"/>
@@ -30,10 +30,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Resource</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Consume</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -146,6 +142,10 @@
   </si>
   <si>
     <t>EffectType</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1129,149 +1129,149 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>11</v>
-      </c>
-      <c r="L2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>8</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>9</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>10</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>11</v>
-      </c>
-      <c r="L3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>28</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>29</v>
       </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
       <c r="F6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" t="s">
         <v>22</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>24</v>
-      </c>
-      <c r="H6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/RPGProject/Assets/Project/Data/ExcelData/InfoEnum.xlsx
+++ b/RPGProject/Assets/Project/Data/ExcelData/InfoEnum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suyb1\Documents\GitHub\RPG\RPGProject\Assets\Project\Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E497EB52-31B1-441F-9242-27BCDA1D0DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA900DB6-E112-45B7-97B8-ACE640971501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1230" yWindow="765" windowWidth="14790" windowHeight="10695" xr2:uid="{69A6533B-D580-4E18-8919-764171C47CAB}"/>
+    <workbookView xWindow="0" yWindow="3060" windowWidth="19905" windowHeight="10695" xr2:uid="{69A6533B-D580-4E18-8919-764171C47CAB}"/>
   </bookViews>
   <sheets>
     <sheet name="CSVEnums" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="77">
   <si>
     <t>ItemType</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -146,6 +146,145 @@
   </si>
   <si>
     <t>Material</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>DefaultCloth</t>
+  </si>
+  <si>
+    <t>Cloth1</t>
+  </si>
+  <si>
+    <t>Cloth2</t>
+  </si>
+  <si>
+    <t>Cloth3</t>
+  </si>
+  <si>
+    <t>Cloth4</t>
+  </si>
+  <si>
+    <t>Cloth5</t>
+  </si>
+  <si>
+    <t>Cloth6</t>
+  </si>
+  <si>
+    <t>Cloth7</t>
+  </si>
+  <si>
+    <t>Cloth8</t>
+  </si>
+  <si>
+    <t>DefaultGlove</t>
+  </si>
+  <si>
+    <t>Glove1</t>
+  </si>
+  <si>
+    <t>Glove2</t>
+  </si>
+  <si>
+    <t>Glove3</t>
+  </si>
+  <si>
+    <t>Glove4</t>
+  </si>
+  <si>
+    <t>Glove5</t>
+  </si>
+  <si>
+    <t>Glove6</t>
+  </si>
+  <si>
+    <t>Crown1</t>
+  </si>
+  <si>
+    <t>Crown2</t>
+  </si>
+  <si>
+    <t>Crown3</t>
+  </si>
+  <si>
+    <t>Crown4</t>
+  </si>
+  <si>
+    <t>Hat1</t>
+  </si>
+  <si>
+    <t>Hat2</t>
+  </si>
+  <si>
+    <t>Hat3</t>
+  </si>
+  <si>
+    <t>Helm2</t>
+  </si>
+  <si>
+    <t>Helm3</t>
+  </si>
+  <si>
+    <t>Helm4</t>
+  </si>
+  <si>
+    <t>Helm5</t>
+  </si>
+  <si>
+    <t>Helm6</t>
+  </si>
+  <si>
+    <t>Helm7</t>
+  </si>
+  <si>
+    <t>DefaultShoes</t>
+  </si>
+  <si>
+    <t>Shoe1</t>
+  </si>
+  <si>
+    <t>Shoe2</t>
+  </si>
+  <si>
+    <t>Shoe3</t>
+  </si>
+  <si>
+    <t>Shoe4</t>
+  </si>
+  <si>
+    <t>Shoe5</t>
+  </si>
+  <si>
+    <t>ShoulderPad1</t>
+  </si>
+  <si>
+    <t>ShoulderPad2</t>
+  </si>
+  <si>
+    <t>ShoulderPad3</t>
+  </si>
+  <si>
+    <t>ShoulderPad4</t>
+  </si>
+  <si>
+    <t>ShoulderPad5</t>
+  </si>
+  <si>
+    <t>ShoulderPad6</t>
+  </si>
+  <si>
+    <t>Belt1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Belt2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Belt3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Helm1</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -739,8 +878,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1118,10 +1260,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C3AF638-3CE2-4C5C-A240-24B6417F96E6}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1135,7 +1277,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -1173,45 +1315,162 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="H3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>47</v>
+      </c>
+      <c r="R3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S3" t="s">
+        <v>49</v>
+      </c>
+      <c r="T3" t="s">
+        <v>50</v>
+      </c>
+      <c r="U3" t="s">
+        <v>51</v>
+      </c>
+      <c r="V3" t="s">
+        <v>52</v>
+      </c>
+      <c r="W3" t="s">
+        <v>53</v>
+      </c>
+      <c r="X3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I3" t="s">
+      <c r="AV3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J3" t="s">
+      <c r="AW3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K3" t="s">
+      <c r="AX3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L3" t="s">
+      <c r="AY3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1228,7 +1487,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1245,7 +1504,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>30</v>
       </c>
